--- a/data/trans_camb/IP07_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP07_R-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-4,71</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10,03</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3,93</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-7,96</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>3,69</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,67</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-4,71</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10,03</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,87</t>
+          <t>-3,35</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,34</t>
+          <t>0,5</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,19; 0,22</t>
+          <t>-13,21; 3,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 11,34</t>
+          <t>2,47; 17,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 6,43</t>
+          <t>-6,26; 14,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 3,34</t>
+          <t>-16,1; 0,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 17,83</t>
+          <t>-3,59; 11,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 15,2</t>
+          <t>-13,64; 5,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 0,43</t>
+          <t>-11,94; -0,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 12,93</t>
+          <t>2,14; 12,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 7,57</t>
+          <t>-6,72; 7,48</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-6,05%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12,89%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,05%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-9,44%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>4,37%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-3,17%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-6,05%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>12,89%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>-3,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,6; 0,23</t>
+          <t>-16,18; 5,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 14,59</t>
+          <t>3,1; 24,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 7,85</t>
+          <t>-7,71; 19,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,18; 4,53</t>
+          <t>-18,48; 0,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,06; 24,32</t>
+          <t>-4,19; 13,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 20,57</t>
+          <t>-15,61; 7,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 0,54</t>
+          <t>-14,38; -0,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,79; 16,74</t>
+          <t>2,56; 15,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 9,68</t>
+          <t>-7,96; 9,35</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,32</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11,03</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,13</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,89</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>10,69</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,7</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,32</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>11,03</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>-0,52</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,34</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 8,14</t>
+          <t>-6,24; 5,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,05; 16,11</t>
+          <t>5,4; 16,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 6,96</t>
+          <t>-5,76; 7,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 5,46</t>
+          <t>-3,84; 7,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,38; 16,25</t>
+          <t>5,04; 16,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 7,5</t>
+          <t>-7,03; 5,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 5,08</t>
+          <t>-3,71; 4,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,89; 15,04</t>
+          <t>7,03; 14,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 5,53</t>
+          <t>-4,63; 5,17</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-0,42%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14,42%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>2,47%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>13,97%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,42%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14,42%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>-0,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 11,01</t>
+          <t>-7,79; 8,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,48; 21,85</t>
+          <t>6,78; 22,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 9,4</t>
+          <t>-7,28; 10,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 7,48</t>
+          <t>-4,84; 10,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,7; 22,17</t>
+          <t>6,32; 21,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 10,23</t>
+          <t>-8,87; 7,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 7,02</t>
+          <t>-4,67; 6,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,74; 20,34</t>
+          <t>8,85; 19,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 7,45</t>
+          <t>-6,02; 6,87</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,02</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8,16</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,41</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-4,69</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>12,56</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,42</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,02</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>8,16</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>-2,93</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,97</t>
+          <t>-1,17</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 4,23</t>
+          <t>-8,16; 7,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,04; 19,66</t>
+          <t>0,28; 15,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,24; 5,79</t>
+          <t>-7,77; 8,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 7,84</t>
+          <t>-13,34; 4,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 16,02</t>
+          <t>5,99; 20,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 8,64</t>
+          <t>-10,36; 6,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 3,74</t>
+          <t>-7,74; 3,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,73; 15,99</t>
+          <t>5,15; 15,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 5,12</t>
+          <t>-7,47; 4,32</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0,02%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11,05%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-6,14%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>16,43%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-3,17%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,02%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>11,05%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>-3,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-1,3%</t>
+          <t>-1,56%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,14; 5,92</t>
+          <t>-10,35; 11,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,27; 28,02</t>
+          <t>0,35; 22,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 8,03</t>
+          <t>-9,93; 12,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 11,24</t>
+          <t>-16,47; 5,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,55; 23,62</t>
+          <t>7,38; 29,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 12,44</t>
+          <t>-12,97; 9,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 4,96</t>
+          <t>-10,11; 4,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,24; 22,3</t>
+          <t>6,5; 21,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 7,11</t>
+          <t>-9,56; 5,98</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-3,56</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8,15</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-3,52</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-2,92</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>8,51</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2,38</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-3,56</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>8,15</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-3,0</t>
+          <t>1,65</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,42</t>
+          <t>-1,07</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 4,08</t>
+          <t>-10,39; 3,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,11; 14,96</t>
+          <t>1,46; 14,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 10,09</t>
+          <t>-12,68; 3,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 2,91</t>
+          <t>-9,86; 4,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,8; 13,92</t>
+          <t>1,89; 14,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 3,84</t>
+          <t>-4,83; 8,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 2,02</t>
+          <t>-8,03; 1,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,3; 12,79</t>
+          <t>3,85; 13,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 5,12</t>
+          <t>-6,86; 3,59</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-4,55%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>10,43%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-4,51%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-3,83%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>11,17%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-4,55%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>10,43%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-3,83%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-0,55%</t>
+          <t>-1,38%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,85; 5,58</t>
+          <t>-12,92; 4,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,7; 21,02</t>
+          <t>1,83; 19,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 13,84</t>
+          <t>-15,89; 4,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 3,8</t>
+          <t>-12,63; 6,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,24; 18,72</t>
+          <t>2,44; 20,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-14,93; 5,02</t>
+          <t>-5,85; 12,03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 2,62</t>
+          <t>-10,19; 2,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,11; 17,22</t>
+          <t>4,86; 17,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 6,91</t>
+          <t>-8,76; 4,8</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,96</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9,22</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-0,95</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-2,35</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>9,59</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,31</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,96</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>9,22</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,61</t>
+          <t>-1,17</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,49</t>
+          <t>-1,07</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 1,33</t>
+          <t>-5,67; 1,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,36; 12,83</t>
+          <t>5,87; 12,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 3,8</t>
+          <t>-5,05; 3,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 1,81</t>
+          <t>-5,88; 1,71</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,05; 13,12</t>
+          <t>6,28; 12,78</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 3,04</t>
+          <t>-4,84; 2,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 0,35</t>
+          <t>-4,84; 0,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7,06; 11,58</t>
+          <t>7,12; 11,62</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 2,19</t>
+          <t>-4,14; 1,47</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-2,55%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>12,03%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-1,24%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-3,03%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>12,36%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-0,4%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-2,55%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>12,03%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-0,79%</t>
+          <t>-1,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-0,63%</t>
+          <t>-1,39%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 1,77</t>
+          <t>-7,18; 1,99</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7,97; 16,88</t>
+          <t>7,43; 16,83</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 4,99</t>
+          <t>-6,59; 4,06</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 2,38</t>
+          <t>-7,47; 2,23</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>7,76; 17,75</t>
+          <t>7,94; 16,92</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 3,99</t>
+          <t>-6,09; 3,41</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 0,47</t>
+          <t>-6,17; 0,59</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>9,07; 15,35</t>
+          <t>9,15; 15,38</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 2,89</t>
+          <t>-5,37; 1,92</t>
         </is>
       </c>
     </row>
